--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E82F68F-0744-4AD1-957D-8A358A1DF0BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0016C963-3E0E-470A-94B7-4F0B7F3C192E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -45,30 +40,15 @@
     <t>None</t>
   </si>
   <si>
-    <t>Domain__c</t>
-  </si>
-  <si>
     <t>Information Technology</t>
   </si>
   <si>
-    <t>Title__c</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>Unit__c</t>
-  </si>
-  <si>
     <t>Dollar ($)</t>
   </si>
   <si>
-    <t>Orientation__c</t>
-  </si>
-  <si>
     <t>Increase</t>
   </si>
   <si>
@@ -76,6 +56,21 @@
   </si>
   <si>
     <t>Automation Runtime KPI</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldDomain__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldUnit__c</t>
+  </si>
+  <si>
+    <t>fieldOrientation__c</t>
   </si>
 </sst>
 </file>
@@ -428,13 +423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,59 +440,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -509,13 +504,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,15 +521,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E82F68F-0744-4AD1-957D-8A358A1DF0BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4621B6-F7E7-4B60-A144-D499A11BFAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -428,13 +428,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,18 +445,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -467,37 +467,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -509,13 +509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BackWardCompatibility_Project\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E82F68F-0744-4AD1-957D-8A358A1DF0BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9294A6F-D7CC-49A7-814E-893FF457598D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -51,24 +51,12 @@
     <t>Information Technology</t>
   </si>
   <si>
-    <t>Title__c</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>Unit__c</t>
-  </si>
-  <si>
     <t>Dollar ($)</t>
   </si>
   <si>
-    <t>Orientation__c</t>
-  </si>
-  <si>
     <t>Increase</t>
   </si>
   <si>
@@ -76,6 +64,21 @@
   </si>
   <si>
     <t>Automation Runtime KPI</t>
+  </si>
+  <si>
+    <t>fieldDomain__c</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldUnit__c</t>
+  </si>
+  <si>
+    <t>fieldOrientation__c</t>
   </si>
 </sst>
 </file>
@@ -428,13 +431,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,59 +448,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -509,13 +512,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -534,7 +537,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4621B6-F7E7-4B60-A144-D499A11BFAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1932358-10AD-4C1F-8096-948673EEA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -76,19 +76,28 @@
   </si>
   <si>
     <t>Automation Runtime KPI</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,8 +120,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +518,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -528,7 +538,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -536,6 +546,9 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductClassic\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E432B9C9-64F2-4732-A5DC-36C383575939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Edition" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,9 +56,6 @@
     <t>Description__c</t>
   </si>
   <si>
-    <t>Automation Test Description</t>
-  </si>
-  <si>
     <t>Unit__c</t>
   </si>
   <si>
@@ -75,13 +71,16 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Automation Runtime KPI</t>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>Educational Details</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -426,7 +425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -464,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -475,7 +474,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -483,10 +482,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -494,10 +493,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -507,7 +506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -534,7 +533,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1932358-10AD-4C1F-8096-948673EEA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBCD79F-70FB-4BE5-95CA-C66D3B10B82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>Description__c</t>
   </si>
   <si>
-    <t>Automation Test Description</t>
-  </si>
-  <si>
     <t>Unit__c</t>
   </si>
   <si>
@@ -75,10 +72,13 @@
     <t>Economic Development</t>
   </si>
   <si>
-    <t>Automation Runtime KPI</t>
-  </si>
-  <si>
     <t>Overview</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>Educational Details</t>
   </si>
 </sst>
 </file>
@@ -141,9 +141,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +181,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -287,7 +287,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,7 +429,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -438,13 +438,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,18 +455,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -477,37 +477,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -519,13 +519,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,18 +536,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
     </row>
   </sheetData>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1932358-10AD-4C1F-8096-948673EEA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777BD008-58C4-4850-AF54-8A4DCAB3A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Edition" sheetId="2" r:id="rId2"/>
+    <sheet name="Grantee_Creation" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,9 +142,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +182,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -287,7 +288,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,7 +430,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -554,4 +555,84 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB2AF0A-3BB2-49E8-94B6-6DFC78E5018C}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationProjects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777BD008-58C4-4850-AF54-8A4DCAB3A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50353548-5B92-4E09-A10B-27B2FA733E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -80,6 +80,48 @@
   </si>
   <si>
     <t>Overview</t>
+  </si>
+  <si>
+    <t>Save and Continue</t>
+  </si>
+  <si>
+    <t>ModalButton</t>
+  </si>
+  <si>
+    <t>PageLayoutButton</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Activate</t>
+  </si>
+  <si>
+    <t>TableAction</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>TabClick</t>
+  </si>
+  <si>
+    <t>TableData</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Field Value1</t>
+  </si>
+  <si>
+    <t>Api</t>
   </si>
 </sst>
 </file>
@@ -438,14 +480,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.90625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,8 +498,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -466,8 +512,11 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -477,8 +526,11 @@
       <c r="C3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -488,8 +540,11 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -499,8 +554,11 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,6 +567,90 @@
       </c>
       <c r="C6" t="s">
         <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -520,13 +662,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -548,7 +690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
     </row>
   </sheetData>
@@ -560,13 +702,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB2AF0A-3BB2-49E8-94B6-6DFC78E5018C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -588,7 +730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -599,7 +741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -610,7 +752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -621,7 +763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777BD008-58C4-4850-AF54-8A4DCAB3A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDACBE1-AF35-4F46-940F-3420AB31DC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationProjects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777BD008-58C4-4850-AF54-8A4DCAB3A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853E23A-6AF7-4ADF-A61C-51E05E54D112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="32">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -80,6 +80,54 @@
   </si>
   <si>
     <t>Overview</t>
+  </si>
+  <si>
+    <t>Save and Continue</t>
+  </si>
+  <si>
+    <t>ModalButton</t>
+  </si>
+  <si>
+    <t>PageLayoutButton</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Activate</t>
+  </si>
+  <si>
+    <t>TableAction</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>TabClick</t>
+  </si>
+  <si>
+    <t>TableData</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Field Value1</t>
+  </si>
+  <si>
+    <t>element Id</t>
+  </si>
+  <si>
+    <t>gdyuasg</t>
+  </si>
+  <si>
+    <t>Edit</t>
   </si>
 </sst>
 </file>
@@ -438,14 +486,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="18.90625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,8 +504,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -466,8 +521,11 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -477,8 +535,11 @@
       <c r="C3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -488,8 +549,11 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -499,8 +563,11 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -509,6 +576,93 @@
       </c>
       <c r="C6" t="s">
         <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -520,13 +674,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -548,7 +702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
     </row>
   </sheetData>
@@ -560,13 +714,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB2AF0A-3BB2-49E8-94B6-6DFC78E5018C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -588,7 +742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -599,7 +753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -610,7 +764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -621,7 +775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/KPI_Field_Values.xlsx
+++ b/src/main/resources/KPI_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationProjects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Product - LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853E23A-6AF7-4ADF-A61C-51E05E54D112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE57DB08-D6B1-4851-B30C-F052E059A8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BDA37FF1-763A-4534-A27A-58B72EDE21C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -487,14 +487,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A4B3D-DD01-4D88-9D0B-35905B1C6D43}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.90625" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -525,7 +525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -539,7 +539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -567,7 +567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -581,7 +581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -609,7 +609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -623,7 +623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -637,7 +637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -651,7 +651,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -674,13 +674,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5008D992-E627-44A6-B9F5-A658F6BB18BD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -702,7 +702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
     </row>
   </sheetData>
@@ -714,13 +714,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB2AF0A-3BB2-49E8-94B6-6DFC78E5018C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -731,7 +731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -742,7 +742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -753,7 +753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -764,7 +764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -775,7 +775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
